--- a/new_bom.xlsx
+++ b/new_bom.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="new_bom" sheetId="1" r:id="rId1"/>
@@ -41,12 +41,12 @@
     <t>Footprint</t>
   </si>
   <si>
+    <t>K3 No.</t>
+  </si>
+  <si>
     <t>VALUE</t>
   </si>
   <si>
-    <t>K3 No.</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -59,36 +59,36 @@
     <t>0603-C</t>
   </si>
   <si>
+    <t>1.1.1.01.02.025GJ</t>
+  </si>
+  <si>
     <t>100nF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.025GJ</t>
-  </si>
-  <si>
     <t>CAP,CER,1nF,5%,50V,C0G,0603</t>
   </si>
   <si>
     <t>C2, C8, C12, C15, C20, C30, C97</t>
   </si>
   <si>
+    <t>1.1.1.01.02.003</t>
+  </si>
+  <si>
     <t>1nF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.003</t>
-  </si>
-  <si>
     <t>CAP,CER,10nF,10%,50V,X7R,0603</t>
   </si>
   <si>
     <t>C3, C4, C7, C13, C23, C32, C54, C61, C130, C171</t>
   </si>
   <si>
+    <t>1.1.1.01.02.002</t>
+  </si>
+  <si>
     <t>10nF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.002</t>
-  </si>
-  <si>
     <t>CAP,CER,100nF,10%,16V,X7R,0402</t>
   </si>
   <si>
@@ -110,12 +110,12 @@
     <t>CAPAE-6*6</t>
   </si>
   <si>
+    <t>1.1.1.01.02.070</t>
+  </si>
+  <si>
     <t>47uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.070</t>
-  </si>
-  <si>
     <t>CAP,CER,4.7uF,10%,50V,X7R,1206</t>
   </si>
   <si>
@@ -125,12 +125,12 @@
     <t>1206-C</t>
   </si>
   <si>
+    <t>1.1.1.01.02.059</t>
+  </si>
+  <si>
     <t>4.7uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.059</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -146,24 +146,24 @@
     <t>C17</t>
   </si>
   <si>
+    <t>1.1.1.01.02.035FH</t>
+  </si>
+  <si>
     <t>100pF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.035FH</t>
-  </si>
-  <si>
     <t>CAP,CER,1uF,10%,50V,X7R,0603</t>
   </si>
   <si>
     <t>C21</t>
   </si>
   <si>
+    <t>1.1.1.01.02.235</t>
+  </si>
+  <si>
     <t>1uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.235</t>
-  </si>
-  <si>
     <t>CAP,CER,10uF,10%,50V,X7R,1206</t>
   </si>
   <si>
@@ -173,12 +173,12 @@
     <t>0805-C</t>
   </si>
   <si>
+    <t>1.1.1.01.02.243</t>
+  </si>
+  <si>
     <t>10uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.243</t>
-  </si>
-  <si>
     <t>C24, C25, C85</t>
   </si>
   <si>
@@ -191,12 +191,12 @@
     <t>C29, C101, C104, C126, C127, C158, C160, C168, C199, C202, C203, C2134, C2135, C2136, C2137, C2138</t>
   </si>
   <si>
+    <t>1.1.1.01.02.187</t>
+  </si>
+  <si>
     <t>2.2uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.187</t>
-  </si>
-  <si>
     <t>CAP,CER,10nF,10%,100V,X7R,0805</t>
   </si>
   <si>
@@ -212,12 +212,12 @@
     <t>C34</t>
   </si>
   <si>
+    <t>1.1.1.01.02.130</t>
+  </si>
+  <si>
     <t>22pF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.130</t>
-  </si>
-  <si>
     <t>C37, C38, C53, C79, C90, C93, C94, C95</t>
   </si>
   <si>
@@ -266,12 +266,12 @@
     <t>C56</t>
   </si>
   <si>
+    <t>1.1.1.01.02.027</t>
+  </si>
+  <si>
     <t>4.7nF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.027</t>
-  </si>
-  <si>
     <t>CAP,CER,100nF,10%,50V,X5R,0402</t>
   </si>
   <si>
@@ -299,12 +299,12 @@
     <t>CAPAE-10*10</t>
   </si>
   <si>
+    <t>1.6.1.01.003.004</t>
+  </si>
+  <si>
     <t>220uF</t>
   </si>
   <si>
-    <t>1.6.1.01.003.004</t>
-  </si>
-  <si>
     <t>CAP,CER,10uF,20%,10V,X5R,0603</t>
   </si>
   <si>
@@ -320,12 +320,12 @@
     <t>C76</t>
   </si>
   <si>
+    <t>1.1.1.01.02.154</t>
+  </si>
+  <si>
     <t>22uF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.154</t>
-  </si>
-  <si>
     <t>CAP,CER,2.2uF,10%,50V,X7R,0805</t>
   </si>
   <si>
@@ -350,12 +350,12 @@
     <t>C99, C109</t>
   </si>
   <si>
+    <t>1.1.1.01.02.163</t>
+  </si>
+  <si>
     <t>22uF DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.02.163</t>
-  </si>
-  <si>
     <t>CAP,CER,22uF,20%,6.3V,X5R,0603</t>
   </si>
   <si>
@@ -383,12 +383,12 @@
     <t>C134, C135</t>
   </si>
   <si>
+    <t>1.1.1.01.02.175</t>
+  </si>
+  <si>
     <t>18pF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.175</t>
-  </si>
-  <si>
     <t>cap,100.00nF,+/-10%,6.3V,X5R,C0402</t>
   </si>
   <si>
@@ -425,12 +425,12 @@
     <t>C163, C164, C166, C167</t>
   </si>
   <si>
+    <t>1.1.1.01.02.177</t>
+  </si>
+  <si>
     <t>33nF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.177</t>
-  </si>
-  <si>
     <t>C172</t>
   </si>
   <si>
@@ -446,12 +446,12 @@
     <t>C183</t>
   </si>
   <si>
+    <t>1.1.1.01.02.231</t>
+  </si>
+  <si>
     <t>470pF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.231</t>
-  </si>
-  <si>
     <t>CAP,CER,1uF,10%,50V,X7R,0805</t>
   </si>
   <si>
@@ -494,12 +494,12 @@
     <t>C281, C282, C2130, C2132</t>
   </si>
   <si>
+    <t>1.1.1.01.02.186</t>
+  </si>
+  <si>
     <t>10pF</t>
   </si>
   <si>
-    <t>1.1.1.01.02.186</t>
-  </si>
-  <si>
     <t>CAP,CER,10nF,10%,50V,X7R,0402</t>
   </si>
   <si>
@@ -554,12 +554,12 @@
     <t>DIOC-5.2*2.6</t>
   </si>
   <si>
+    <t>1.1.1.01.03.053</t>
+  </si>
+  <si>
     <t>SK310B</t>
   </si>
   <si>
-    <t>1.1.1.01.03.053</t>
-  </si>
-  <si>
     <t>D,SW,1,200mA,250V,1,SOD323/HIGH-VOLTAGE</t>
   </si>
   <si>
@@ -569,12 +569,12 @@
     <t>SOD-2.5*0.95</t>
   </si>
   <si>
+    <t>1.1.1.01.05.113</t>
+  </si>
+  <si>
     <t>BAS21HT1G</t>
   </si>
   <si>
-    <t>1.1.1.01.05.113</t>
-  </si>
-  <si>
     <t>贴片二极管 BAV99 250MW/100V (S0T-23)</t>
   </si>
   <si>
@@ -584,12 +584,12 @@
     <t>SOT-23</t>
   </si>
   <si>
+    <t>1.6.1.01.004.004</t>
+  </si>
+  <si>
     <t>BAV99</t>
   </si>
   <si>
-    <t>1.6.1.01.004.004</t>
-  </si>
-  <si>
     <t>D,SW,1,100mA,25V,1X2DFN-2P/HIGH-SPEED</t>
   </si>
   <si>
@@ -599,24 +599,24 @@
     <t>X2DFN-2</t>
   </si>
   <si>
+    <t>1.1.1.01.03.112</t>
+  </si>
+  <si>
     <t>SM0130MB</t>
   </si>
   <si>
-    <t>1.1.1.01.03.112</t>
-  </si>
-  <si>
     <t>D,RECT,1A,1000V,1,SMA-W</t>
   </si>
   <si>
     <t>D5</t>
   </si>
   <si>
+    <t>1.1.1.01.03.013A</t>
+  </si>
+  <si>
     <t>M7-01-W001</t>
   </si>
   <si>
-    <t>1.1.1.01.03.013A</t>
-  </si>
-  <si>
     <t>D,RECT,3A,1000V,1，DO-214AB(SMC)</t>
   </si>
   <si>
@@ -626,12 +626,12 @@
     <t>DIOC-8*6</t>
   </si>
   <si>
+    <t>1.1.1.01.03.102</t>
+  </si>
+  <si>
     <t>SS36</t>
   </si>
   <si>
-    <t>1.1.1.01.03.102</t>
-  </si>
-  <si>
     <t>D12</t>
   </si>
   <si>
@@ -644,12 +644,12 @@
     <t>D16</t>
   </si>
   <si>
+    <t>1.1.1.01.03.126</t>
+  </si>
+  <si>
     <t>AD-RB550V-30</t>
   </si>
   <si>
-    <t>1.1.1.01.03.126</t>
-  </si>
-  <si>
     <t>Data Matrix Area</t>
   </si>
   <si>
@@ -668,12 +668,12 @@
     <t>1206-R</t>
   </si>
   <si>
+    <t>1.1.1.01.01.548</t>
+  </si>
+  <si>
     <t>FUSE</t>
   </si>
   <si>
-    <t>1.1.1.01.01.548</t>
-  </si>
-  <si>
     <t>FBEAD,350mR,600R@100MHz,25%,400mA,0603</t>
   </si>
   <si>
@@ -683,12 +683,12 @@
     <t>FBC-0603, 0603-R</t>
   </si>
   <si>
+    <t>1.1.1.01.09.015</t>
+  </si>
+  <si>
     <t>600R</t>
   </si>
   <si>
-    <t>1.1.1.01.09.015</t>
-  </si>
-  <si>
     <t>F BEAD,350mR,600R@100MHz,25%,400mA,0603</t>
   </si>
   <si>
@@ -707,12 +707,12 @@
     <t>0402-R</t>
   </si>
   <si>
+    <t>1.1.1.01.09.101</t>
+  </si>
+  <si>
     <t>1kΩ</t>
   </si>
   <si>
-    <t>1.1.1.01.09.101</t>
-  </si>
-  <si>
     <t>Fidicial Mark</t>
   </si>
   <si>
@@ -731,12 +731,12 @@
     <t>D4S10E-40MA5</t>
   </si>
   <si>
+    <t>1.1.1.01.14.008</t>
+  </si>
+  <si>
     <t>1107042500（D4S11M-40MA5-D）</t>
   </si>
   <si>
-    <t>1.1.1.01.14.008</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
@@ -752,12 +752,12 @@
     <t>CONN-HSC-4</t>
   </si>
   <si>
+    <t>1.1.1.02.14.121</t>
+  </si>
+  <si>
     <t>TAK-A4LMD</t>
   </si>
   <si>
-    <t>1.1.1.02.14.121</t>
-  </si>
-  <si>
     <t>CON FPC,10P,1R,0.5MM,SMT/LOWER,FLIP</t>
   </si>
   <si>
@@ -779,12 +779,12 @@
     <t>INDC7.7*7.2</t>
   </si>
   <si>
+    <t>1.1.1.01.09.042A</t>
+  </si>
+  <si>
     <t>22uH</t>
   </si>
   <si>
-    <t>1.1.1.01.09.042A</t>
-  </si>
-  <si>
     <t>IND,PWR,4.7uH,6A,7*6.6</t>
   </si>
   <si>
@@ -794,12 +794,12 @@
     <t>INDC7.2*6.6</t>
   </si>
   <si>
+    <t>1.1.1.01.09.049</t>
+  </si>
+  <si>
     <t>4.7uH</t>
   </si>
   <si>
-    <t>1.1.1.01.09.049</t>
-  </si>
-  <si>
     <t>IND,PWR,15uH@100KHz,20%,2.83A,10.5*10.3</t>
   </si>
   <si>
@@ -809,12 +809,12 @@
     <t>INDM-10.5*10.3</t>
   </si>
   <si>
+    <t>1.1.1.01.09.012A</t>
+  </si>
+  <si>
     <t>15uH</t>
   </si>
   <si>
-    <t>1.1.1.01.09.012A</t>
-  </si>
-  <si>
     <t>TDK PWR 700Ω@100MHz 20% 4A 7.0*6.0</t>
   </si>
   <si>
@@ -824,12 +824,12 @@
     <t>PMF7060</t>
   </si>
   <si>
+    <t>1.1.1.01.09.052A</t>
+  </si>
+  <si>
     <t>ACM7060-701-2PL</t>
   </si>
   <si>
-    <t>1.1.1.01.09.052A</t>
-  </si>
-  <si>
     <t>IND,PWR,1uH@100KHz,20%,6A,5*5*2</t>
   </si>
   <si>
@@ -839,12 +839,12 @@
     <t>SMD4x4x2</t>
   </si>
   <si>
+    <t>1.1.1.01.09.123</t>
+  </si>
+  <si>
     <t>10uH</t>
   </si>
   <si>
-    <t>1.1.1.01.09.123</t>
-  </si>
-  <si>
     <t>IND,PWR,0.47uH,6A,2.5*2.0</t>
   </si>
   <si>
@@ -854,12 +854,12 @@
     <t>INDC-2.5*2</t>
   </si>
   <si>
+    <t>1.1.1.01.09.091</t>
+  </si>
+  <si>
     <t>0.47uH</t>
   </si>
   <si>
-    <t>1.1.1.01.09.091</t>
-  </si>
-  <si>
     <t>IND,CHOCK,90R@100MHz,25%,330mA,2.0*1.2*1.0</t>
   </si>
   <si>
@@ -869,12 +869,12 @@
     <t>INDC-CHOKE-0805</t>
   </si>
   <si>
+    <t>1.1.1.01.09.035</t>
+  </si>
+  <si>
     <t>90R</t>
   </si>
   <si>
-    <t>1.1.1.01.09.035</t>
-  </si>
-  <si>
     <t>L20</t>
   </si>
   <si>
@@ -887,12 +887,12 @@
     <t>INDM-9*6-4</t>
   </si>
   <si>
+    <t>1.1.1.01.09.003A</t>
+  </si>
+  <si>
     <t>DNP(ACM4532-601-2P)</t>
   </si>
   <si>
-    <t>1.1.1.01.09.003A</t>
-  </si>
-  <si>
     <t>Header, 3-Pin</t>
   </si>
   <si>
@@ -920,12 +920,12 @@
     <t>TO-2.29P-10*6.6-3</t>
   </si>
   <si>
+    <t>1.1.1.01.03.118</t>
+  </si>
+  <si>
     <t>YJD18GP10A</t>
   </si>
   <si>
-    <t>1.1.1.01.03.118</t>
-  </si>
-  <si>
     <t>MOSFET,N,115mA,60V,7.5R,SOT23</t>
   </si>
   <si>
@@ -935,36 +935,36 @@
     <t>SOT-0.95P-2.9*2.4-3-L</t>
   </si>
   <si>
+    <t>1.1.1.01.03.071</t>
+  </si>
+  <si>
     <t>2N7002</t>
   </si>
   <si>
-    <t>1.1.1.01.03.071</t>
-  </si>
-  <si>
     <t>BIP,PNP,500mA,150V,1,SOT-23(TO-236)/HIGH-VOLTAGE</t>
   </si>
   <si>
     <t>Q4</t>
   </si>
   <si>
+    <t>1.6.1.01.004.003</t>
+  </si>
+  <si>
     <t>MMBT5401LT1G</t>
   </si>
   <si>
-    <t>1.6.1.01.004.003</t>
-  </si>
-  <si>
     <t>MOSFET,P,4.3A,12V,50mR,1,SOT23</t>
   </si>
   <si>
     <t>Q5</t>
   </si>
   <si>
+    <t>1.1.1.01.03.072</t>
+  </si>
+  <si>
     <t>IRLML6401 DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.03.072</t>
-  </si>
-  <si>
     <t>Q6</t>
   </si>
   <si>
@@ -989,108 +989,108 @@
     <t>0603-R</t>
   </si>
   <si>
+    <t>1.1.1.01.01.259</t>
+  </si>
+  <si>
     <t>100K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.259</t>
-  </si>
-  <si>
     <t>RES,GEN,10K,5%,100mW,0603</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
+    <t>1.1.1.01.01.065</t>
+  </si>
+  <si>
     <t>10K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.065</t>
-  </si>
-  <si>
     <t>RES,GEN,1K,5%,100mW,0603</t>
   </si>
   <si>
     <t>R4, R7, R54</t>
   </si>
   <si>
+    <t>1.1.1.01.01.064GJ</t>
+  </si>
+  <si>
     <t>1K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.064GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,8.06K,1%,100mW,0603</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
+    <t>1.1.1.01.01.167-GJ</t>
+  </si>
+  <si>
     <t>8.06K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.167-GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,1.5K,1%,100mW,0603</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
+    <t>1.1.1.01.01.268</t>
+  </si>
+  <si>
     <t>1.5K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.268</t>
-  </si>
-  <si>
     <t>RES,GEN,44.2kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
     <t>R8</t>
   </si>
   <si>
+    <t>1.1.1.01.01.506</t>
+  </si>
+  <si>
     <t>44.2kΩ</t>
   </si>
   <si>
-    <t>1.1.1.01.01.506</t>
-  </si>
-  <si>
     <t>RES,GEN,2K,1%,100mW,0603</t>
   </si>
   <si>
     <t>R11, R45</t>
   </si>
   <si>
+    <t>1.1.1.01.01.159GJJM</t>
+  </si>
+  <si>
     <t>2K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.159GJJM</t>
-  </si>
-  <si>
     <t>RES,GEN,12K,1%,100mW,0603</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
+    <t>1.1.1.01.01.276</t>
+  </si>
+  <si>
     <t>12K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.276</t>
-  </si>
-  <si>
     <t>RES,GEN,10R,5%,62.5mW,0603</t>
   </si>
   <si>
     <t>R13</t>
   </si>
   <si>
+    <t>1.1.1.01.01.307</t>
+  </si>
+  <si>
     <t>10R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.307</t>
-  </si>
-  <si>
     <t>RES,GEN,1K,1%,100mW,0603</t>
   </si>
   <si>
@@ -1112,48 +1112,48 @@
     <t>R16</t>
   </si>
   <si>
+    <t>1.1.1.01.01.314</t>
+  </si>
+  <si>
     <t>47K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.314</t>
-  </si>
-  <si>
     <t>RES,GEN,56K,1%,62.5mW,0603</t>
   </si>
   <si>
     <t>R18, R40, R51, R66, R96, R99</t>
   </si>
   <si>
+    <t>1.1.1.01.01.294</t>
+  </si>
+  <si>
     <t>56K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.294</t>
-  </si>
-  <si>
     <t>RES MF 100 OHM 1/2W 1% 1206</t>
   </si>
   <si>
     <t>R19</t>
   </si>
   <si>
+    <t>1.1.1.01.01.033GJ</t>
+  </si>
+  <si>
     <t>100R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.033GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,4.7K,5%,62.5mW,0402</t>
   </si>
   <si>
     <t>R20, R22, R33, R36, R67, R68, R70, R155, R156, R164, R165, R166, R167, R171, R174, R313, R314</t>
   </si>
   <si>
+    <t>1.1.1.01.01.311</t>
+  </si>
+  <si>
     <t>4.7K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.311</t>
-  </si>
-  <si>
     <t>RES,GEN,10K,1%,100mW,0603</t>
   </si>
   <si>
@@ -1196,24 +1196,24 @@
     <t>R26, R27, R49, R53, R116, R117, R124, R129, R149, R150, R1702, R1703</t>
   </si>
   <si>
+    <t>1.1.1.01.01.269</t>
+  </si>
+  <si>
     <t>0R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.269</t>
-  </si>
-  <si>
     <t>RES,GEN,200K,1%,62.5mW,0402</t>
   </si>
   <si>
     <t>R28</t>
   </si>
   <si>
+    <t>1.1.1.01.01.498</t>
+  </si>
+  <si>
     <t>200K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.498</t>
-  </si>
-  <si>
     <t>RES,GEN,100K,5%,62.5mW,0402</t>
   </si>
   <si>
@@ -1229,48 +1229,48 @@
     <t>R31</t>
   </si>
   <si>
+    <t>1.1.1.01.01.469</t>
+  </si>
+  <si>
     <t>3.92KΩ</t>
   </si>
   <si>
-    <t>1.1.1.01.01.469</t>
-  </si>
-  <si>
     <t>RES,GEN,73.2K,1%,100mW,0603</t>
   </si>
   <si>
     <t>R32</t>
   </si>
   <si>
+    <t>1.1.1.01.01.255</t>
+  </si>
+  <si>
     <t>73.2K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.255</t>
-  </si>
-  <si>
     <t>RES,GEN,200R,1%,250mW,1206</t>
   </si>
   <si>
     <t>R34, R35</t>
   </si>
   <si>
+    <t>1.1.1.01.01.036-GJ</t>
+  </si>
+  <si>
     <t>200R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.036-GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,0R,5%,62.5mW,0402</t>
   </si>
   <si>
     <t>R37, R38, R160, R163, R1105</t>
   </si>
   <si>
+    <t>1.1.1.01.01.309</t>
+  </si>
+  <si>
     <t>0R DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.309</t>
-  </si>
-  <si>
     <t>R39, R41, R73, R75, R76, R84, R89, R114, R128, R130, R131, R138, R139, R158, R294, R1401, R1402, R1608, R2105, R2114, R2115, R2117, R2118, R2120, R2121, R2122</t>
   </si>
   <si>
@@ -1280,48 +1280,48 @@
     <t>R50, R52</t>
   </si>
   <si>
+    <t>1.1.1.01.01.089</t>
+  </si>
+  <si>
     <t>60.4R DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.089</t>
-  </si>
-  <si>
     <t>RES,GEN,2.2K,5%,250mW,1206</t>
   </si>
   <si>
     <t>R55, R58, R65, R79, R91, R93, R95, R113, R146</t>
   </si>
   <si>
+    <t>1.1.1.01.01.151</t>
+  </si>
+  <si>
     <t>2.2K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.151</t>
-  </si>
-  <si>
     <t>RES,GEN,820K,1%,62.5mW,0603</t>
   </si>
   <si>
     <t>R57, R90, R92, R144</t>
   </si>
   <si>
+    <t>1.1.1.01.01.367</t>
+  </si>
+  <si>
     <t>820K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.367</t>
-  </si>
-  <si>
     <t>RES,GEN,107K,1%,,0402</t>
   </si>
   <si>
     <t>R59</t>
   </si>
   <si>
+    <t>1.1.1.01.01.386</t>
+  </si>
+  <si>
     <t>107K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.386</t>
-  </si>
-  <si>
     <t>RES,GEN,10k,1%,62.5mW,0402</t>
   </si>
   <si>
@@ -1346,36 +1346,36 @@
     <t>R63</t>
   </si>
   <si>
+    <t>1.1.1.01.01.504</t>
+  </si>
+  <si>
     <t>182K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.504</t>
-  </si>
-  <si>
     <t>RES,GEN,1M,1%,62.5mW,0603</t>
   </si>
   <si>
     <t>R64, R98, R115</t>
   </si>
   <si>
+    <t>1.1.1.01.01.301</t>
+  </si>
+  <si>
     <t>1M</t>
   </si>
   <si>
-    <t>1.1.1.01.01.301</t>
-  </si>
-  <si>
     <t>RES,GEN,31.6K,1%,,0402</t>
   </si>
   <si>
     <t>R69</t>
   </si>
   <si>
+    <t>1.1.1.01.01.387</t>
+  </si>
+  <si>
     <t>31.6K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.387</t>
-  </si>
-  <si>
     <t>R71, R122, R161</t>
   </si>
   <si>
@@ -1394,24 +1394,24 @@
     <t>R74</t>
   </si>
   <si>
+    <t>1.1.1.01.01.427</t>
+  </si>
+  <si>
     <t>75K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.427</t>
-  </si>
-  <si>
     <t>RES,GEN,1MR,1%,62.5mW,0402</t>
   </si>
   <si>
     <t>R78</t>
   </si>
   <si>
+    <t>1.1.1.01.01.349</t>
+  </si>
+  <si>
     <t>1MR</t>
   </si>
   <si>
-    <t>1.1.1.01.01.349</t>
-  </si>
-  <si>
     <t>RES,GEN,200K,1%,100mW,0603</t>
   </si>
   <si>
@@ -1427,12 +1427,12 @@
     <t>R82, R86, R87, R88, R107, R108</t>
   </si>
   <si>
+    <t>1.1.1.01.01.426</t>
+  </si>
+  <si>
     <t>5.1K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.426</t>
-  </si>
-  <si>
     <t>RES,GEN,4.7K,5%,100mW,0603</t>
   </si>
   <si>
@@ -1451,12 +1451,12 @@
     <t>RESC-2512</t>
   </si>
   <si>
+    <t>1.1.1.01.01.211</t>
+  </si>
+  <si>
     <t>330R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.211</t>
-  </si>
-  <si>
     <t>R101, R136, R140, R141, R142, R283, R284, R288</t>
   </si>
   <si>
@@ -1475,12 +1475,12 @@
     <t>R106</t>
   </si>
   <si>
+    <t>1.1.1.01.01.529</t>
+  </si>
+  <si>
     <t>20K_1%</t>
   </si>
   <si>
-    <t>1.1.1.01.01.529</t>
-  </si>
-  <si>
     <t>R110, R173</t>
   </si>
   <si>
@@ -1493,12 +1493,12 @@
     <t>R111</t>
   </si>
   <si>
+    <t>1.1.1.01.01.121GJ</t>
+  </si>
+  <si>
     <t>6.04K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.121GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,100R,5%,100mW,0603</t>
   </si>
   <si>
@@ -1511,12 +1511,12 @@
     <t>R118</t>
   </si>
   <si>
+    <t>1.1.1.01.01.460</t>
+  </si>
+  <si>
     <t>10Ω</t>
   </si>
   <si>
-    <t>1.1.1.01.01.460</t>
-  </si>
-  <si>
     <t>RES,GEN,1R,5%,100mW,0603</t>
   </si>
   <si>
@@ -1526,12 +1526,12 @@
     <t>0805-R</t>
   </si>
   <si>
+    <t>1.1.1.01.01.063</t>
+  </si>
+  <si>
     <t>1R DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.063</t>
-  </si>
-  <si>
     <t>R125</t>
   </si>
   <si>
@@ -1541,24 +1541,24 @@
     <t>R127</t>
   </si>
   <si>
+    <t>1.1.1.01.01.439</t>
+  </si>
+  <si>
     <t>250K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.439</t>
-  </si>
-  <si>
     <t>RES,GEN,45.3kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
     <t>R133</t>
   </si>
   <si>
+    <t>1.1.1.01.01.472</t>
+  </si>
+  <si>
     <t>45.3KΩ</t>
   </si>
   <si>
-    <t>1.1.1.01.01.472</t>
-  </si>
-  <si>
     <t>R137</t>
   </si>
   <si>
@@ -1568,12 +1568,12 @@
     <t>R147, R148, R316, R318, R1300, R1806, R1807</t>
   </si>
   <si>
+    <t>1.1.1.01.01.312</t>
+  </si>
+  <si>
     <t>22R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.312</t>
-  </si>
-  <si>
     <t>R152</t>
   </si>
   <si>
@@ -1586,36 +1586,36 @@
     <t>R153</t>
   </si>
   <si>
+    <t>1.1.1.01.01.169-GJ</t>
+  </si>
+  <si>
     <t>20K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.169-GJ</t>
-  </si>
-  <si>
     <t>RES,GEN,47K,1%,62.5mW,0603</t>
   </si>
   <si>
     <t>R159</t>
   </si>
   <si>
+    <t>1.1.1.01.01.298</t>
+  </si>
+  <si>
     <t>47K DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.298</t>
-  </si>
-  <si>
     <t>RES,GEN,20K,5%,100mW,0603</t>
   </si>
   <si>
     <t>R162</t>
   </si>
   <si>
+    <t>1.1.1.01.01.101-GJ</t>
+  </si>
+  <si>
     <t>20K DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.101-GJ</t>
-  </si>
-  <si>
     <t>R169</t>
   </si>
   <si>
@@ -1625,12 +1625,12 @@
     <t>R170</t>
   </si>
   <si>
+    <t>1.1.1.01.01.160-GJ</t>
+  </si>
+  <si>
     <t>5.1K DNP</t>
   </si>
   <si>
-    <t>1.1.1.01.01.160-GJ</t>
-  </si>
-  <si>
     <t>R172</t>
   </si>
   <si>
@@ -1643,24 +1643,24 @@
     <t>R1100</t>
   </si>
   <si>
+    <t>1.1.1.01.01.310</t>
+  </si>
+  <si>
     <t>33R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.310</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,133R,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
     <t>R1400</t>
   </si>
   <si>
+    <t>1.1.1.01.01.526</t>
+  </si>
+  <si>
     <t>133R</t>
   </si>
   <si>
-    <t>1.1.1.01.01.526</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,2K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
@@ -1676,60 +1676,60 @@
     <t>R2102</t>
   </si>
   <si>
+    <t>1.1.1.01.01.549</t>
+  </si>
+  <si>
     <t>82K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.549</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,120K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
     <t>R2103</t>
   </si>
   <si>
+    <t>1.1.1.01.01.496</t>
+  </si>
+  <si>
     <t>120K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.496</t>
-  </si>
-  <si>
     <t>RES,GEN,2.2kΩ,1%,62.5mW,0402</t>
   </si>
   <si>
     <t>R2108, R2110</t>
   </si>
   <si>
+    <t>1.1.1.01.01.432</t>
+  </si>
+  <si>
     <t>2.2KΩ</t>
   </si>
   <si>
-    <t>1.1.1.01.01.432</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,110K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
     <t>R2113</t>
   </si>
   <si>
+    <t>1.1.1.01.01.434</t>
+  </si>
+  <si>
     <t>110K</t>
   </si>
   <si>
-    <t>1.1.1.01.01.434</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,49.9K,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
     <t>R2116</t>
   </si>
   <si>
+    <t>1.1.1.01.01.425</t>
+  </si>
+  <si>
     <t>49.9k</t>
   </si>
   <si>
-    <t>1.1.1.01.01.425</t>
-  </si>
-  <si>
     <t>通用厚膜电阻,240R,+/-1%,R0402,1/16W.</t>
   </si>
   <si>
@@ -1766,12 +1766,12 @@
     <t>SHIELD_CAN_CLIP$2F$PTV0703B</t>
   </si>
   <si>
+    <t>1.1.2.310.006</t>
+  </si>
+  <si>
     <t>SC / PTV0703B 屏蔽夹</t>
   </si>
   <si>
-    <t>1.1.2.310.006</t>
-  </si>
-  <si>
     <t>SPEAKER,94dB,400Hz-10KHz,50R,34MM</t>
   </si>
   <si>
@@ -1781,12 +1781,12 @@
     <t>SPK-3P-36*15.9</t>
   </si>
   <si>
+    <t>1.1.1.02.09.027</t>
+  </si>
+  <si>
     <t>UGSP3750-06</t>
   </si>
   <si>
-    <t>1.1.1.02.09.027</t>
-  </si>
-  <si>
     <t>TVS,3.3V,300mW,2,SOD-923</t>
   </si>
   <si>
@@ -1796,12 +1796,12 @@
     <t>SOD-1*0.6</t>
   </si>
   <si>
+    <t>1.1.1.01.03.073</t>
+  </si>
+  <si>
     <t>ESD9B5.0ST5G</t>
   </si>
   <si>
-    <t>1.1.1.01.03.073</t>
-  </si>
-  <si>
     <t>TVS4, TVS5</t>
   </si>
   <si>
@@ -1874,12 +1874,12 @@
     <t>QFN-0.5P-9*9-64-EPAD</t>
   </si>
   <si>
+    <t>1.1.1.01.05.299</t>
+  </si>
+  <si>
     <t>DS90UB940-Q1</t>
   </si>
   <si>
-    <t>1.1.1.01.05.299</t>
-  </si>
-  <si>
     <t>IC,CAN Tranceiver,High-speed/Standby mode,SO8</t>
   </si>
   <si>
@@ -1889,12 +1889,12 @@
     <t>SOIC-1.27P-6*5-8</t>
   </si>
   <si>
+    <t>1.1.1.01.05.478</t>
+  </si>
+  <si>
     <t>TCAN1042DRQ1</t>
   </si>
   <si>
-    <t>1.1.1.01.05.478</t>
-  </si>
-  <si>
     <t>IC,RTC,±5*10E-6,QFN10/with Temperature Compensation</t>
   </si>
   <si>
@@ -1904,12 +1904,12 @@
     <t>QFN-0.7P-3.2*2.5-10</t>
   </si>
   <si>
+    <t>1.1.1.01.05.208A</t>
+  </si>
+  <si>
     <t>INS5609</t>
   </si>
   <si>
-    <t>1.1.1.01.05.208A</t>
-  </si>
-  <si>
     <t>MPQ20051DQ-AEC1</t>
   </si>
   <si>
@@ -1940,12 +1940,12 @@
     <t>SOT-0.65P-2*2.1-5</t>
   </si>
   <si>
+    <t>1.1.1.01.05.261</t>
+  </si>
+  <si>
     <t>NLVVHC1GT126DF1G</t>
   </si>
   <si>
-    <t>1.1.1.01.05.261</t>
-  </si>
-  <si>
     <t>U16</t>
   </si>
   <si>
@@ -1955,12 +1955,12 @@
     <t>U22</t>
   </si>
   <si>
+    <t>1.1.1.01.05.307</t>
+  </si>
+  <si>
     <t>BR24G16FJ-3GTE2</t>
   </si>
   <si>
-    <t>1.1.1.01.05.307</t>
-  </si>
-  <si>
     <t>U1000</t>
   </si>
   <si>
@@ -2000,12 +2000,12 @@
     <t>FBGA153_0P5_11P5X13</t>
   </si>
   <si>
+    <t>1.1.1.01.05.486</t>
+  </si>
+  <si>
     <t>KLM8G1GEUF-B04Q057</t>
   </si>
   <si>
-    <t>1.1.1.01.05.486</t>
-  </si>
-  <si>
     <t>CON,32P,2R,TE BLUE,TE BLUE-32</t>
   </si>
   <si>
@@ -2015,12 +2015,12 @@
     <t>CONN-TE BLUE-2137614-2-32</t>
   </si>
   <si>
+    <t>1.1.1.02.14.059</t>
+  </si>
+  <si>
     <t>966658-2 /2137614-2</t>
   </si>
   <si>
-    <t>1.1.1.02.14.059</t>
-  </si>
-  <si>
     <t>XTD Logo</t>
   </si>
   <si>
@@ -2039,24 +2039,24 @@
     <t>XTALC-3.2*2.5-4</t>
   </si>
   <si>
+    <t>1.1.1.01.08.017</t>
+  </si>
+  <si>
     <t>24MHz</t>
   </si>
   <si>
-    <t>1.1.1.01.08.017</t>
-  </si>
-  <si>
     <t>XTAL,25MHz, ±10PPM,3.2*2.5</t>
   </si>
   <si>
     <t>Y2</t>
   </si>
   <si>
+    <t>1.1.1.01.08.029</t>
+  </si>
+  <si>
     <t>25MHz</t>
   </si>
   <si>
-    <t>1.1.1.01.08.029</t>
-  </si>
-  <si>
     <t>XTAL,32.768KHz,±10PPM,3.2*1.5*0.8</t>
   </si>
   <si>
@@ -2066,22 +2066,22 @@
     <t>XTALC-3.2*1.5-2</t>
   </si>
   <si>
+    <t>1.1.1.01.08.022</t>
+  </si>
+  <si>
     <t>32.768KHz</t>
   </si>
   <si>
-    <t>1.1.1.01.08.022</t>
-  </si>
-  <si>
     <t>TVS,27V,225mW,2,SOT-23</t>
   </si>
   <si>
     <t>Z1, Z2</t>
   </si>
   <si>
+    <t>1.1.1.01.03.015</t>
+  </si>
+  <si>
     <t>MMBZ27VCLT1G</t>
-  </si>
-  <si>
-    <t>1.1.1.01.03.015</t>
   </si>
 </sst>
 </file>
@@ -3473,8 +3473,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="24.075" customWidth="1"/>
-    <col min="3" max="5" width="14.5833333333333" customWidth="1"/>
+    <col min="2" max="2" width="36.5" customWidth="1"/>
+    <col min="3" max="3" width="14.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="22.125" customWidth="1"/>
+    <col min="5" max="5" width="14.5833333333333" customWidth="1"/>
     <col min="6" max="6" width="9.975" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3569,10 +3571,10 @@
         <v>21</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F5" s="10">
         <v>50</v>
@@ -3628,10 +3630,10 @@
       <c r="C8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="9"/>
+      <c r="E8" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="9"/>
       <c r="F8" s="10">
         <v>1</v>
       </c>
@@ -3707,10 +3709,10 @@
         <v>21</v>
       </c>
       <c r="D12" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>50</v>
       </c>
       <c r="F12" s="10">
         <v>3</v>
@@ -3747,10 +3749,10 @@
         <v>46</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F14" s="10">
         <v>5</v>
@@ -3787,10 +3789,10 @@
         <v>30</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="F16" s="10">
         <v>8</v>
@@ -3807,10 +3809,10 @@
         <v>21</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="F17" s="10">
         <v>1</v>
@@ -3827,10 +3829,10 @@
         <v>21</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="F18" s="10">
         <v>1</v>
@@ -3847,10 +3849,10 @@
         <v>21</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F19" s="10">
         <v>7</v>
@@ -3867,10 +3869,10 @@
         <v>8</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="F20" s="10">
         <v>2</v>
@@ -3907,10 +3909,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>82</v>
+        <v>10</v>
       </c>
       <c r="F22" s="10">
         <v>4</v>
@@ -3927,10 +3929,10 @@
         <v>46</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="F23" s="10">
         <v>3</v>
@@ -3967,10 +3969,10 @@
         <v>8</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>47</v>
+        <v>93</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="F25" s="10">
         <v>10</v>
@@ -4007,10 +4009,10 @@
         <v>46</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="F27" s="10">
         <v>11</v>
@@ -4027,10 +4029,10 @@
         <v>46</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="F28" s="10">
         <v>1</v>
@@ -4067,10 +4069,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F30" s="10">
         <v>10</v>
@@ -4087,10 +4089,10 @@
         <v>8</v>
       </c>
       <c r="D31" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>111</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>14</v>
       </c>
       <c r="F31" s="10">
         <v>3</v>
@@ -4107,10 +4109,10 @@
         <v>21</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>114</v>
+        <v>14</v>
       </c>
       <c r="F32" s="10">
         <v>7</v>
@@ -4146,10 +4148,10 @@
       <c r="C34" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="17" t="s">
         <v>22</v>
       </c>
+      <c r="E34" s="9"/>
       <c r="F34" s="10">
         <v>23</v>
       </c>
@@ -4180,10 +4182,10 @@
       <c r="C36" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="9"/>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="17" t="s">
         <v>125</v>
       </c>
+      <c r="E36" s="9"/>
       <c r="F36" s="10">
         <v>9</v>
       </c>
@@ -4199,10 +4201,10 @@
         <v>8</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="F37" s="10">
         <v>2</v>
@@ -4239,10 +4241,10 @@
         <v>8</v>
       </c>
       <c r="D39" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="17" t="s">
         <v>134</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="F39" s="10">
         <v>1</v>
@@ -4259,10 +4261,10 @@
         <v>8</v>
       </c>
       <c r="D40" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="17" t="s">
         <v>134</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>18</v>
       </c>
       <c r="F40" s="10">
         <v>1</v>
@@ -4299,10 +4301,10 @@
         <v>46</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="F42" s="10">
         <v>3</v>
@@ -4319,10 +4321,10 @@
         <v>46</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>145</v>
+        <v>32</v>
       </c>
       <c r="F43" s="10">
         <v>2</v>
@@ -4359,10 +4361,10 @@
         <v>46</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="F45" s="10">
         <v>1</v>
@@ -4379,10 +4381,10 @@
         <v>8</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="F46" s="10">
         <v>5</v>
@@ -4419,10 +4421,10 @@
         <v>21</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F48" s="10">
         <v>3</v>
@@ -4439,10 +4441,10 @@
         <v>21</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F49" s="10">
         <v>23</v>
@@ -4459,10 +4461,10 @@
         <v>21</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="F50" s="10">
         <v>2</v>
@@ -4479,10 +4481,10 @@
         <v>21</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="F51" s="10">
         <v>15</v>
@@ -4499,10 +4501,10 @@
         <v>8</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>47</v>
+        <v>166</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="F52" s="10">
         <v>2</v>
@@ -4518,10 +4520,10 @@
       <c r="C53" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="17" t="s">
+      <c r="D53" s="17" t="s">
         <v>169</v>
       </c>
+      <c r="E53" s="9"/>
       <c r="F53" s="10">
         <v>1</v>
       </c>
@@ -4536,10 +4538,10 @@
       <c r="C54" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="17" t="s">
+      <c r="D54" s="17" t="s">
         <v>22</v>
       </c>
+      <c r="E54" s="9"/>
       <c r="F54" s="10">
         <v>16</v>
       </c>
@@ -4675,10 +4677,10 @@
         <v>173</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="F61" s="10">
         <v>1</v>
@@ -4882,10 +4884,10 @@
       <c r="C72" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="D72" s="9"/>
-      <c r="E72" s="17" t="s">
+      <c r="D72" s="17" t="s">
         <v>245</v>
       </c>
+      <c r="E72" s="9"/>
       <c r="F72" s="10">
         <v>1</v>
       </c>
@@ -5040,10 +5042,10 @@
       <c r="C80" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="D80" s="9"/>
-      <c r="E80" s="17" t="s">
-        <v>280</v>
-      </c>
+      <c r="D80" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="E80" s="9"/>
       <c r="F80" s="10">
         <v>1</v>
       </c>
@@ -5191,10 +5193,10 @@
         <v>300</v>
       </c>
       <c r="D88" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E88" s="17" t="s">
         <v>312</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>302</v>
       </c>
       <c r="F88" s="10">
         <v>1</v>
@@ -5211,10 +5213,10 @@
         <v>211</v>
       </c>
       <c r="D89" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="E89" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="E89" s="17" t="s">
-        <v>315</v>
       </c>
       <c r="F89" s="10">
         <v>1</v>
@@ -5411,10 +5413,10 @@
         <v>318</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="F99" s="10">
         <v>1</v>
@@ -5431,10 +5433,10 @@
         <v>318</v>
       </c>
       <c r="D100" s="17" t="s">
+        <v>357</v>
+      </c>
+      <c r="E100" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="E100" s="17" t="s">
-        <v>357</v>
       </c>
       <c r="F100" s="10">
         <v>3</v>
@@ -5531,10 +5533,10 @@
         <v>318</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>376</v>
+        <v>324</v>
       </c>
       <c r="F105" s="10">
         <v>2</v>
@@ -5551,10 +5553,10 @@
         <v>224</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>323</v>
+        <v>379</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>379</v>
+        <v>324</v>
       </c>
       <c r="F106" s="10">
         <v>16</v>
@@ -5571,10 +5573,10 @@
         <v>224</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>327</v>
+        <v>382</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="F107" s="10">
         <v>6</v>
@@ -5591,10 +5593,10 @@
         <v>224</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="F108" s="10">
         <v>1</v>
@@ -5651,10 +5653,10 @@
         <v>224</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>319</v>
+        <v>396</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="F111" s="10">
         <v>3</v>
@@ -5751,10 +5753,10 @@
         <v>224</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="F116" s="10">
         <v>26</v>
@@ -5851,10 +5853,10 @@
         <v>224</v>
       </c>
       <c r="D121" s="17" t="s">
+        <v>432</v>
+      </c>
+      <c r="E121" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="E121" s="17" t="s">
-        <v>432</v>
       </c>
       <c r="F121" s="10">
         <v>4</v>
@@ -5871,10 +5873,10 @@
         <v>224</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>368</v>
+        <v>435</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>435</v>
+        <v>369</v>
       </c>
       <c r="F122" s="10">
         <v>3</v>
@@ -5951,10 +5953,10 @@
         <v>224</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>327</v>
+        <v>449</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>449</v>
+        <v>328</v>
       </c>
       <c r="F126" s="10">
         <v>3</v>
@@ -5971,10 +5973,10 @@
         <v>224</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>347</v>
+        <v>451</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>451</v>
+        <v>348</v>
       </c>
       <c r="F127" s="10">
         <v>1</v>
@@ -6031,10 +6033,10 @@
         <v>318</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>392</v>
+        <v>462</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>462</v>
+        <v>393</v>
       </c>
       <c r="F130" s="10">
         <v>2</v>
@@ -6071,10 +6073,10 @@
         <v>318</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>372</v>
+        <v>469</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>469</v>
+        <v>373</v>
       </c>
       <c r="F132" s="10">
         <v>1</v>
@@ -6111,10 +6113,10 @@
         <v>224</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>323</v>
+        <v>432</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>432</v>
+        <v>324</v>
       </c>
       <c r="F134" s="10">
         <v>8</v>
@@ -6191,10 +6193,10 @@
         <v>224</v>
       </c>
       <c r="D138" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="E138" s="17" t="s">
         <v>484</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>379</v>
       </c>
       <c r="F138" s="10">
         <v>2</v>
@@ -6231,10 +6233,10 @@
         <v>224</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>368</v>
+        <v>435</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>435</v>
+        <v>369</v>
       </c>
       <c r="F140" s="10">
         <v>5</v>
@@ -6351,10 +6353,10 @@
         <v>224</v>
       </c>
       <c r="D146" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="E146" s="17" t="s">
         <v>35</v>
-      </c>
-      <c r="E146" s="17" t="s">
-        <v>412</v>
       </c>
       <c r="F146" s="10">
         <v>1</v>
@@ -6391,10 +6393,10 @@
         <v>318</v>
       </c>
       <c r="D148" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="E148" s="17" t="s">
         <v>515</v>
-      </c>
-      <c r="E148" s="17" t="s">
-        <v>462</v>
       </c>
       <c r="F148" s="10">
         <v>1</v>
@@ -6471,10 +6473,10 @@
         <v>318</v>
       </c>
       <c r="D152" s="17" t="s">
+        <v>376</v>
+      </c>
+      <c r="E152" s="17" t="s">
         <v>484</v>
-      </c>
-      <c r="E152" s="17" t="s">
-        <v>376</v>
       </c>
       <c r="F152" s="10">
         <v>1</v>
@@ -6511,10 +6513,10 @@
         <v>318</v>
       </c>
       <c r="D154" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="E154" s="17" t="s">
         <v>534</v>
-      </c>
-      <c r="E154" s="17" t="s">
-        <v>365</v>
       </c>
       <c r="F154" s="10">
         <v>1</v>
@@ -6571,10 +6573,10 @@
         <v>224</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>343</v>
+        <v>545</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>545</v>
+        <v>344</v>
       </c>
       <c r="F157" s="10">
         <v>2</v>
@@ -6690,10 +6692,10 @@
       <c r="C163" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D163" s="9"/>
-      <c r="E163" s="17" t="s">
+      <c r="D163" s="17" t="s">
         <v>568</v>
       </c>
+      <c r="E163" s="9"/>
       <c r="F163" s="10">
         <v>4</v>
       </c>
@@ -6708,10 +6710,10 @@
       <c r="C164" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="D164" s="9"/>
-      <c r="E164" s="17" t="s">
+      <c r="D164" s="17" t="s">
         <v>571</v>
       </c>
+      <c r="E164" s="9"/>
       <c r="F164" s="10">
         <v>2</v>
       </c>
@@ -6727,10 +6729,10 @@
         <v>574</v>
       </c>
       <c r="D165" s="17" t="s">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="E165" s="17" t="s">
-        <v>575</v>
+        <v>538</v>
       </c>
       <c r="F165" s="10">
         <v>3</v>
@@ -6807,10 +6809,10 @@
         <v>587</v>
       </c>
       <c r="D169" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="E169" s="17" t="s">
         <v>591</v>
-      </c>
-      <c r="E169" s="17" t="s">
-        <v>589</v>
       </c>
       <c r="F169" s="10">
         <v>2</v>
@@ -6826,10 +6828,10 @@
       <c r="C170" s="17" t="s">
         <v>594</v>
       </c>
-      <c r="D170" s="9"/>
-      <c r="E170" s="17" t="s">
+      <c r="D170" s="17" t="s">
         <v>595</v>
       </c>
+      <c r="E170" s="9"/>
       <c r="F170" s="10">
         <v>1</v>
       </c>
@@ -6844,10 +6846,10 @@
       <c r="C171" s="17" t="s">
         <v>598</v>
       </c>
-      <c r="D171" s="9"/>
-      <c r="E171" s="17" t="s">
+      <c r="D171" s="17" t="s">
         <v>599</v>
       </c>
+      <c r="E171" s="9"/>
       <c r="F171" s="10">
         <v>1</v>
       </c>
@@ -6862,10 +6864,10 @@
       <c r="C172" s="17" t="s">
         <v>601</v>
       </c>
-      <c r="D172" s="9"/>
-      <c r="E172" s="17" t="s">
+      <c r="D172" s="17" t="s">
         <v>602</v>
       </c>
+      <c r="E172" s="9"/>
       <c r="F172" s="10">
         <v>1</v>
       </c>
@@ -6880,10 +6882,10 @@
       <c r="C173" s="17" t="s">
         <v>605</v>
       </c>
-      <c r="D173" s="9"/>
-      <c r="E173" s="17" t="s">
+      <c r="D173" s="17" t="s">
         <v>606</v>
       </c>
+      <c r="E173" s="9"/>
       <c r="F173" s="10">
         <v>1</v>
       </c>
@@ -6979,10 +6981,10 @@
         <v>628</v>
       </c>
       <c r="D178" s="17" t="s">
+        <v>629</v>
+      </c>
+      <c r="E178" s="17" t="s">
         <v>626</v>
-      </c>
-      <c r="E178" s="17" t="s">
-        <v>629</v>
       </c>
       <c r="F178" s="10">
         <v>1</v>
@@ -6998,10 +7000,10 @@
       <c r="C179" s="17" t="s">
         <v>631</v>
       </c>
-      <c r="D179" s="9"/>
-      <c r="E179" s="17" t="s">
+      <c r="D179" s="17" t="s">
         <v>632</v>
       </c>
+      <c r="E179" s="9"/>
       <c r="F179" s="10">
         <v>1</v>
       </c>
@@ -7036,10 +7038,10 @@
       <c r="C181" s="17" t="s">
         <v>628</v>
       </c>
-      <c r="D181" s="9"/>
-      <c r="E181" s="17" t="s">
+      <c r="D181" s="17" t="s">
         <v>629</v>
       </c>
+      <c r="E181" s="9"/>
       <c r="F181" s="10">
         <v>1</v>
       </c>
@@ -7074,10 +7076,10 @@
       <c r="C183" s="17" t="s">
         <v>644</v>
       </c>
-      <c r="D183" s="9"/>
-      <c r="E183" s="17" t="s">
+      <c r="D183" s="17" t="s">
         <v>645</v>
       </c>
+      <c r="E183" s="9"/>
       <c r="F183" s="10">
         <v>1</v>
       </c>
@@ -7092,10 +7094,10 @@
       <c r="C184" s="17" t="s">
         <v>647</v>
       </c>
-      <c r="D184" s="9"/>
-      <c r="E184" s="17" t="s">
+      <c r="D184" s="17" t="s">
         <v>648</v>
       </c>
+      <c r="E184" s="9"/>
       <c r="F184" s="10">
         <v>1</v>
       </c>
@@ -7110,10 +7112,10 @@
       <c r="C185" s="17" t="s">
         <v>651</v>
       </c>
-      <c r="D185" s="9"/>
-      <c r="E185" s="17" t="s">
+      <c r="D185" s="17" t="s">
         <v>652</v>
       </c>
+      <c r="E185" s="9"/>
       <c r="F185" s="10">
         <v>2</v>
       </c>
